--- a/UTCUTS/A1_Inputs/A-I_Horizon_Configuration.xlsx
+++ b/UTCUTS/A1_Inputs/A-I_Horizon_Configuration.xlsx
@@ -617,5 +617,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{849FFC8F-CA26-4FCF-A766-259741A46B4D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D2CF430-9FDE-4049-990B-D07AF02061FC}"/>
 </file>